--- a/artfynd/A 34418-2025 artfynd.xlsx
+++ b/artfynd/A 34418-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>66791902</v>
+        <v>66791950</v>
       </c>
       <c r="B2" t="n">
-        <v>77259</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80461</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>228912</v>
+        <v>6462</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -717,10 +712,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>481187.0639923461</v>
+        <v>481220</v>
       </c>
       <c r="R2" t="n">
-        <v>6693924.240376659</v>
+        <v>6693962</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -750,19 +745,14 @@
           <t>2017-07-14</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2017-07-14</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>På gammal asp.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -793,37 +783,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>66791950</v>
+        <v>66791887</v>
       </c>
       <c r="B3" t="n">
-        <v>78596</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79085</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6462</v>
+        <v>228912</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -835,10 +820,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>481219.9491226317</v>
+        <v>481229</v>
       </c>
       <c r="R3" t="n">
-        <v>6693962.144825736</v>
+        <v>6693860</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -868,24 +853,9 @@
           <t>2017-07-14</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2017-07-14</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>På gammal asp.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -916,15 +886,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>66791913</v>
+        <v>66791902</v>
       </c>
       <c r="B4" t="n">
-        <v>77259</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79085</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -958,10 +923,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>481264.8379523144</v>
+        <v>481187</v>
       </c>
       <c r="R4" t="n">
-        <v>6693926.80541313</v>
+        <v>6693924</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -991,19 +956,9 @@
           <t>2017-07-14</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2017-07-14</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1027,6 +982,109 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr">
+        <is>
+          <t>Kontinuitetsskogar Gyllbergens skogsrike</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>66791913</v>
+      </c>
+      <c r="B5" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Omr. 42 Orsen N, Dlr</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>481265</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6693927</v>
+      </c>
+      <c r="S5" t="n">
+        <v>5</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Gagnef</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Floda</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2017-07-14</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2017-07-14</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Lars-Erik Nilsson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Lars-Erik Nilsson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
         <is>
           <t>Kontinuitetsskogar Gyllbergens skogsrike</t>
         </is>

--- a/artfynd/A 34418-2025 artfynd.xlsx
+++ b/artfynd/A 34418-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AZ5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -780,6 +785,11 @@
           <t>Kontinuitetsskogar Gyllbergens skogsrike</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/66791950</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -883,6 +893,11 @@
           <t>Kontinuitetsskogar Gyllbergens skogsrike</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/66791887</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -986,6 +1001,11 @@
           <t>Kontinuitetsskogar Gyllbergens skogsrike</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/66791902</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1089,8 +1109,19 @@
           <t>Kontinuitetsskogar Gyllbergens skogsrike</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/66791913</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>